--- a/artfynd/A 30727-2024 artfynd.xlsx
+++ b/artfynd/A 30727-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129126847</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129126845</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30727-2024 artfynd.xlsx
+++ b/artfynd/A 30727-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096827</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129126847</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129126845</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129126848</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30727-2024 artfynd.xlsx
+++ b/artfynd/A 30727-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129096827</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129126847</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129126845</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129126848</v>
       </c>
       <c r="B5" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30727-2024 artfynd.xlsx
+++ b/artfynd/A 30727-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129126847</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129126845</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
